--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260911.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260911.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>9.62%</t>
+          <t>9.65%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.34%</t>
+          <t>9.41%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.49%</t>
+          <t>6.53%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>6.05%</t>
+          <t>5.69%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.21%</t>
+          <t>4.17%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.95%</t>
+          <t>4.02%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.91%</t>
+          <t>3.99%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.76%</t>
+          <t>3.68%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.12%</t>
+          <t>3.21%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>3.08%</t>
         </is>
       </c>
     </row>
@@ -836,51 +836,51 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>3.06%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>64,742,000</t>
+          <t>354,020,964</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.92%</t>
+          <t>2.85%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>354,020,964</t>
+          <t>64,742,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>2.80%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>2.77%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.69%</t>
+          <t>2.58%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>2.55%</t>
         </is>
       </c>
     </row>
@@ -968,51 +968,51 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>2.54%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>99,718,442</t>
+          <t>131,081,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>2.47%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>131,081,000</t>
+          <t>99,718,442</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.45%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.43%</t>
+          <t>2.45%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>2.39%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>2.28%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.14%</t>
+          <t>2.17%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>1.94%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>1.93%</t>
         </is>
       </c>
     </row>
@@ -1195,44 +1195,44 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>53,388,000</t>
+          <t>272,189,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.80%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>272,189,000</t>
+          <t>53,388,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.76%</t>
+          <t>1.80%</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>10,820,832,523</t>
+          <t>10,525,159,087</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr"/>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>6,684,039,190</t>
+          <t>6,443,020,390</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>-580,571,263</t>
+          <t>-341,614,308</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
